--- a/themes/consumerLoan.xlsx
+++ b/themes/consumerLoan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,141 +450,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Подать заявку на потребительский кредит можно [тут]({{$temp.ConsumerLoanLink}})</t>
+          <t xml:space="preserve">      • Минимальный возраст — 23 года (для клиентов, имеющих одобренное кредитное предложения от банка — 21 год)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Подать заявку на потребительский кредит можно [тут]({{$temp.ConsumerLoanLink}}).</t>
+          <t xml:space="preserve">      • Минимальный возраст — 23 года (для клиентов, имеющих одобренное кредитное предложение от банка — 21 год)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«предложения» исправлено на «предложение» — согласование с «одобренное» (винительный падеж, ед. число)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Agree: Для оформления заявки на потребительский кредит с условиями из персонального предложения перейдите по [ссылке]({{ $temp.OpenOfferCreditLink }})</t>
+          <t xml:space="preserve">      • Максимальный возраст на момент окончания срока кредита - 70 лет (для клиентов, имеющих одобренное кредитное предложения от банка — 75 лет)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Agree: Для оформления заявки на потребительский кредит с условиями из персонального предложения перейдите по [ссылке]({{ $temp.OpenOfferCreditLink }}).</t>
+          <t xml:space="preserve">      • Максимальный возраст на момент окончания срока кредита — 70 лет (для клиентов, имеющих одобренное кредитное предложение от банка — 75 лет)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - "Подать заявку на потребительский кредит можно [тут]({{$temp.ConsumerLoanLink}})"</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - "Подать заявку на потребительский кредит можно [тут]({{$temp.ConsumerLoanLink}})."</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Минимальный возраст — 23 года (для клиентов, имеющих одобренное кредитное предложения от банка — 21 год)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Минимальный возраст — 23 года (для клиентов, имеющих одобренное кредитное предложение от банка — 21 год)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>«предложения» исправлено на «предложение» — согласование с «одобренное» (винительный падеж, ед. число)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>90</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Максимальный возраст на момент окончания срока кредита - 70 лет (для клиентов, имеющих одобренное кредитное предложения от банка — 75 лет)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Максимальный возраст на момент окончания срока кредита — 70 лет (для клиентов, имеющих одобренное кредитное предложение от банка — 75 лет)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>дефис заменён на тире; «предложения» исправлено на «предложение» — согласование с «одобренное»</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>146</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FinalAnswer: Также отправляю вам ссылку на документ с подробным описанием [тарифного плана](https://uralsib.ru/api/directory-engine/files/rates/potreb_standart_300426_yzxkm9gt.pdf)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FinalAnswer: Также отправляю вам ссылку на документ с подробным описанием [тарифного плана](https://uralsib.ru/api/directory-engine/files/rates/potreb_standart_300426_yzxkm9gt.pdf).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>161</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Оформить заявку на потребительский кредит вы можете по [ссылке]({{$temp.ConsumerLoanLink}})</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Оформить заявку на потребительский кредит вы можете по [ссылке]({{$temp.ConsumerLoanLink}}).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
